--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,23 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Hitesh Git hub\Data-Analytics\Data-Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2A9EF0A-263B-4D2E-A18A-A34152101858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44FC941-DCDD-4678-B755-D30CE79A2149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9877E020-D8B8-4241-860F-9552F5AF7DF9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9877E020-D8B8-4241-860F-9552F5AF7DF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$K$9:$K$12</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$L$8</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$L$9:$L$12</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$80:$B$83</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$C$79</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$C$80:$C$83</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$80:$B$83</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$C$79</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$C$80:$C$83</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$80:$B$83</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$C$79</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$C$80:$C$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="75">
   <si>
     <t>Batch</t>
   </si>
@@ -194,12 +189,93 @@
   <si>
     <t>Games</t>
   </si>
+  <si>
+    <t>Sr No.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Hitesh</t>
+  </si>
+  <si>
+    <t>Prithvi</t>
+  </si>
+  <si>
+    <t>Pankaj</t>
+  </si>
+  <si>
+    <t>Ravindra</t>
+  </si>
+  <si>
+    <t>Hetvi</t>
+  </si>
+  <si>
+    <t>Jyoti</t>
+  </si>
+  <si>
+    <t>Shivam</t>
+  </si>
+  <si>
+    <t>Om</t>
+  </si>
+  <si>
+    <t>Donald</t>
+  </si>
+  <si>
+    <t>Hardik</t>
+  </si>
+  <si>
+    <t>hitu@gmail</t>
+  </si>
+  <si>
+    <t>prith@gmail.com</t>
+  </si>
+  <si>
+    <t>panku@gmail.com</t>
+  </si>
+  <si>
+    <t>Rav@gmail.com</t>
+  </si>
+  <si>
+    <t>het@gmail.com</t>
+  </si>
+  <si>
+    <t>Jyoti@gmail.com</t>
+  </si>
+  <si>
+    <t>shivam@gmail.com</t>
+  </si>
+  <si>
+    <t>om@gmail.com</t>
+  </si>
+  <si>
+    <t>Don@gmail.com</t>
+  </si>
+  <si>
+    <t>Hard@gmail.com</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,8 +295,22 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,8 +329,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -263,11 +365,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -284,6 +401,22 @@
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,6 +679,640 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="175508399"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Marks</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$O$5:$O$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Math</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Science</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>English</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Computer</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Social</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$5:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>68</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B078-4BCB-B7A9-3C2E32D4366D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="608686831"/>
+        <c:axId val="608693071"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="608686831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="608693071"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="608693071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="608686831"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Students</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$15:$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>DA_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DA_02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DA_03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>DA_04</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$15:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E10C-451E-B666-B85B2FAA2FDC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Students</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$15:$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>DA_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DA_02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DA_03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>DA_04</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$15:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E10C-451E-B666-B85B2FAA2FDC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="635586831"/>
+        <c:axId val="635588495"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="635586831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="635588495"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="635588495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="635586831"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1272,6 +2039,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-FA24-43FA-8EA6-E741461597D0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1287,6 +2059,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-FA24-43FA-8EA6-E741461597D0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1302,6 +2079,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-FA24-43FA-8EA6-E741461597D0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1317,6 +2099,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-FA24-43FA-8EA6-E741461597D0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1332,6 +2119,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-FA24-43FA-8EA6-E741461597D0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1614,6 +2406,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2E1A-44E3-8659-A1D40D34DB5C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1629,6 +2426,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2E1A-44E3-8659-A1D40D34DB5C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1644,6 +2446,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2E1A-44E3-8659-A1D40D34DB5C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1659,6 +2466,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2E1A-44E3-8659-A1D40D34DB5C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3177,6 +3989,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4F3A-40A1-9F9F-3020FD46B5D1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3192,6 +4009,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4F3A-40A1-9F9F-3020FD46B5D1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3207,6 +4029,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4F3A-40A1-9F9F-3020FD46B5D1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -3222,6 +4049,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-4F3A-40A1-9F9F-3020FD46B5D1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3426,10 +4258,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3440,7 +4272,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{B30DBD6C-3B40-4A3A-A637-5E649033A369}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Students</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3505,6 +4337,86 @@
 </file>
 
 <file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4544,6 +5456,1014 @@
       <cs:styleClr val="auto"/>
     </cs:lnRef>
     <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -9433,6 +11353,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A164944-BDB7-1ECD-51C9-21FBA3F9CC8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44F71F7A-4674-03C6-475F-D1AB2B04C975}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9733,7 +11725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDDB447-47A7-470E-858F-97C21358EC92}">
-  <dimension ref="B3:L148"/>
+  <dimension ref="B3:P148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
@@ -9742,40 +11734,64 @@
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="O4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>78</v>
       </c>
+      <c r="O5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="2">
+        <v>78</v>
+      </c>
     </row>
-    <row r="6" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="3">
         <v>85</v>
       </c>
+      <c r="O6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="3">
+        <v>85</v>
+      </c>
     </row>
-    <row r="7" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>72</v>
       </c>
+      <c r="O7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="2">
+        <v>72</v>
+      </c>
     </row>
-    <row r="8" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
@@ -9784,8 +11800,14 @@
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
+      <c r="O8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" s="3">
+        <v>90</v>
+      </c>
     </row>
-    <row r="9" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
@@ -9794,21 +11816,27 @@
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
+      <c r="O9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="2">
+        <v>68</v>
+      </c>
     </row>
-    <row r="10" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>0</v>
       </c>
@@ -9816,40 +11844,72 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="2">
         <v>25</v>
       </c>
+      <c r="O15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="3">
         <v>30</v>
       </c>
+      <c r="O16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" s="2">
+        <v>25</v>
+      </c>
     </row>
-    <row r="17" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="2">
         <v>28</v>
       </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3">
+        <v>30</v>
+      </c>
     </row>
-    <row r="18" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="3">
         <v>22</v>
       </c>
+      <c r="O18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="2">
+        <v>28</v>
+      </c>
     </row>
-    <row r="29" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P19" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:16" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>18</v>
       </c>
@@ -9857,7 +11917,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>20</v>
       </c>
@@ -9865,7 +11925,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>21</v>
       </c>
@@ -10205,4 +12265,239 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DE2E85-C1B5-4F77-B49E-1164590D57B7}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="9">
+        <v>30</v>
+      </c>
+      <c r="E2" s="9">
+        <v>28905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="9">
+        <v>32</v>
+      </c>
+      <c r="E3" s="9">
+        <v>27771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="9">
+        <v>26</v>
+      </c>
+      <c r="E4" s="9">
+        <v>30423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="9">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9">
+        <v>30849</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="9">
+        <v>30</v>
+      </c>
+      <c r="E6" s="9">
+        <v>34514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="9">
+        <v>31</v>
+      </c>
+      <c r="E7" s="9">
+        <v>33214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="9">
+        <v>31</v>
+      </c>
+      <c r="E8" s="9">
+        <v>30643</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="9">
+        <v>26</v>
+      </c>
+      <c r="E9" s="9">
+        <v>28957</v>
+      </c>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="9">
+        <v>26</v>
+      </c>
+      <c r="E10" s="9">
+        <v>27758</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="9">
+        <v>29</v>
+      </c>
+      <c r="E11" s="9">
+        <v>31124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8">
+        <f>SUM(D2:D11)</f>
+        <v>291</v>
+      </c>
+      <c r="E12" s="8">
+        <f>SUM(E2:E11)</f>
+        <v>304158</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A12:C12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{9919F5AB-34E2-4DAF-9C86-73B55A83D742}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{D5AC665B-67BD-4ECE-BEB5-1DF552DEF05D}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{AD290E98-4184-4E5C-9720-8C9F516E375F}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{B4D6FAA5-FA3A-4BB5-80A2-17BB1F33C8C8}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{52326334-384C-45E2-8F77-B2BCCC6873EF}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{3975140A-7B87-464F-8716-6CA1B052EB95}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{CECE7301-A1C3-47A1-B5DF-9867EB1E5E7F}"/>
+    <hyperlink ref="C11" r:id="rId8" xr:uid="{9F4F66E5-F7EA-458B-BF79-CA1D168212BF}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{0C495226-40B7-44D5-AD67-17CDB405F305}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
+</worksheet>
 </file>